--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhiwuzou/Documents/cursor/football-betting-python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F7976A-9799-8B40-87E9-592FEBD88C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BBDBDF-D6DD-B54F-928B-AA734FFC4911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16760" yWindow="-22860" windowWidth="28100" windowHeight="20160" xr2:uid="{7F2FA93A-CCBE-594E-86E8-44FA899D3C52}"/>
   </bookViews>
@@ -20,21 +20,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
-  <si>
-    <t>联赛</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>主队</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>客队</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -59,6 +51,10 @@
   </si>
   <si>
     <t>最新凯利指数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间点</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -1033,10 +1029,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E539AB0A-6FA0-ED4E-9CE1-BC49466DC3DD}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1044,48 +1040,45 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16" customHeight="1">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16" customHeight="1">
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
       <c r="J2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" t="s">
         <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
